--- a/30_Asset/SNFramework.xlsx
+++ b/30_Asset/SNFramework.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shinj\OneDrive\ドキュメント\Creation\ソフト開発\WindowsProject\30_Asset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81515F0C-8C41-495C-90FA-215A5A2B5B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B04EC60-5D27-4856-B7C1-28CEC3EACF57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16371" yWindow="0" windowWidth="16629" windowHeight="18600" firstSheet="14" activeTab="15" xr2:uid="{70336C66-D1CA-48C0-83F2-0D9D170A84BC}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18720" firstSheet="14" activeTab="15" xr2:uid="{70336C66-D1CA-48C0-83F2-0D9D170A84BC}"/>
   </bookViews>
   <sheets>
     <sheet name="目次" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="310">
   <si>
     <t>システム構成</t>
     <rPh sb="4" eb="6">
@@ -2701,6 +2701,28 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>SND3D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SND2D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Direct3D11を制御する</t>
+    <rPh sb="11" eb="13">
+      <t>セイギョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Direct2Dを制御する</t>
+    <rPh sb="9" eb="11">
+      <t>セイギョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -38360,7 +38382,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E418DDC-5C4E-4C27-8205-BD9C57C2BA64}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="3.5" defaultRowHeight="18.45"/>
   <cols>
     <col min="1" max="2" width="3.5" style="3"/>
@@ -38403,147 +38425,165 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="C6" s="7"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="C7" s="5" t="s">
-        <v>17</v>
-      </c>
+      <c r="C7" s="6"/>
       <c r="D7" s="4" t="s">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>92</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="C8" s="6"/>
       <c r="D8" s="4" t="s">
-        <v>84</v>
+        <v>307</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>94</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="C9" s="6"/>
-      <c r="D9" s="4" t="s">
-        <v>85</v>
+      <c r="C9" s="7"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="C10" s="5" t="s">
+        <v>17</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="C11" s="6"/>
       <c r="D11" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="C12" s="6"/>
       <c r="D12" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="C13" s="6"/>
       <c r="D13" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="C14" s="6"/>
       <c r="D14" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="C15" s="6"/>
       <c r="D15" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="C16" s="6"/>
       <c r="D16" s="4" t="s">
-        <v>296</v>
+        <v>89</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>303</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="3:5">
       <c r="C17" s="6"/>
       <c r="D17" s="4" t="s">
-        <v>299</v>
+        <v>90</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>300</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="3:5">
       <c r="C18" s="6"/>
       <c r="D18" s="4" t="s">
-        <v>297</v>
+        <v>91</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>301</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="3:5">
       <c r="C19" s="6"/>
       <c r="D19" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20" spans="3:5">
       <c r="C20" s="6"/>
       <c r="D20" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5">
+      <c r="C21" s="6"/>
+      <c r="D21" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="22" spans="3:5">
+      <c r="C22" s="6"/>
+      <c r="D22" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E22" s="4" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="21" spans="3:5">
-      <c r="C21" s="7"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="3:5">
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
+    <row r="23" spans="3:5">
+      <c r="C23" s="7"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="3:5">
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
